--- a/dados-catalago-pcm-interno/nomes_usuais_epi.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais_epi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="534" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36ABD90E-E997-4234-BEDE-9FF3EC9004A2}"/>
+  <xr:revisionPtr revIDLastSave="550" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9298AD97-D02C-4C17-9112-081B2B42CFF0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-24600" yWindow="4200" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="116">
   <si>
     <t>material</t>
   </si>
@@ -172,9 +172,6 @@
     <t>LUVA MULTITATO ( G )</t>
   </si>
   <si>
-    <t>LUVA MULTITATO ( GG )</t>
-  </si>
-  <si>
     <t>LUVA LATEX AMAR SOFT ( G )</t>
   </si>
   <si>
@@ -196,24 +193,6 @@
     <t>AVENTAL BARBEIRO MARFE 732CBA</t>
   </si>
   <si>
-    <t>MACACAO LAVADOR ( M )</t>
-  </si>
-  <si>
-    <t>MACACAO LAVADOR ( G )</t>
-  </si>
-  <si>
-    <t>MACACAO LAVADOR ( P )</t>
-  </si>
-  <si>
-    <t>MACACAO LAVADOR ( GG )</t>
-  </si>
-  <si>
-    <t>MACACAO LAVADOR ( XG )</t>
-  </si>
-  <si>
-    <t>MACACAO LAVADOR ( XXG )</t>
-  </si>
-  <si>
     <t>CANELEIRA</t>
   </si>
   <si>
@@ -382,30 +361,6 @@
     <t>Sinalização</t>
   </si>
   <si>
-    <t>CALÇA POSTO ( XG )</t>
-  </si>
-  <si>
-    <t>CALÇA POSTO ( GG )</t>
-  </si>
-  <si>
-    <t>CALÇA POSTO ( G )</t>
-  </si>
-  <si>
-    <t>CALÇA POSTO ( M )</t>
-  </si>
-  <si>
-    <t>CALÇA POSTO ( P )</t>
-  </si>
-  <si>
-    <t>CAMISA OPERACIONAL POSTO  ( G )</t>
-  </si>
-  <si>
-    <t>CAMISA OPERACIONAL POSTO  ( P )</t>
-  </si>
-  <si>
-    <t>Uniformes Posto</t>
-  </si>
-  <si>
     <t>CALÇA OPERACIONAL MECÂNICA ( GG )</t>
   </si>
   <si>
@@ -431,60 +386,6 @@
   </si>
   <si>
     <t>Uniformes Mecânica</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI CAREC LG AZ CELEST ( EXG )</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI CAREC LG AZ CELEST ( EG )</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI CAREC LG AZ CELEST ( GG )</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI CAREC LG AZ CELEST ( G )</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI CAREC LG AZ CELEST ( M )</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI CAREC LG AZ CELEST ( P )</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI POLO PIQ AZ C/LOGO ( EXG )</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI POLO PIQ AZ C/LOGO ( EG )</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI POLO PIQ AZ C/LOGO ( GG )</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI POLO PIQ AZ C/LOGO ( G )</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI POLO PIQ AZ C/LOGO ( M )</t>
-  </si>
-  <si>
-    <t>CAMISETA UNI POLO PIQ AZ C/LOGO ( P )</t>
-  </si>
-  <si>
-    <t>Uniformes Motorista</t>
-  </si>
-  <si>
-    <t>LUVA SEG NY/ELAST/NBR DANNY/DA35530E(EXCLUSIVO POSTO) ( G )</t>
-  </si>
-  <si>
-    <t>LUVA SEG NY/ELAST/NBR DANNY/DA35530E(EXCLUSIVO POSTO) ( M )</t>
-  </si>
-  <si>
-    <t>LUVA SEG NY/ELAST/NBR DANNY/DA35530E(EXCLUSIVO POSTO) ( P )</t>
-  </si>
-  <si>
-    <t>LUVA SEG NY/ELAST/NBR DANNY/DA35530E(EXCLUSIVO POSTO) ( XG )</t>
-  </si>
-  <si>
-    <t>LUVA SEG NY/ELAST/NBR DANNY/DA35530E(EXCLUSIVO POSTO) ( XXG )</t>
   </si>
   <si>
     <t>LUVA SEG AG MEC/QUIM NBR PROT CAP/NF15 ( P )</t>
@@ -881,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H706"/>
+  <dimension ref="A1:H675"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
@@ -1186,7 +1087,7 @@
         <v>39</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1197,7 +1098,7 @@
         <v>40</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1208,7 +1109,7 @@
         <v>41</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1219,1073 +1120,860 @@
         <v>42</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="9"/>
+      <c r="A31" s="9">
+        <v>77391</v>
+      </c>
       <c r="B31" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
-        <v>77391</v>
+        <v>1020001294</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>44</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
-        <v>1020001294</v>
+        <v>1020001273</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
-        <v>1020001273</v>
+        <v>1020001304</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
-        <v>1020002762</v>
+        <v>1020001237</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
-        <v>1020002766</v>
+        <v>1020001198</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
-        <v>1020002765</v>
+        <v>1020001037</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
-        <v>1020002763</v>
+        <v>1020000874</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
-        <v>1020002764</v>
+        <v>1030000556</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>147</v>
+        <v>52</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
-        <v>1020001304</v>
+        <v>1020001071</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
-        <v>1020001237</v>
+        <v>1020001092</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>148</v>
+        <v>54</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
-        <v>1020001198</v>
+        <v>1020001568</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="9"/>
+      <c r="A43" s="9">
+        <v>1020001569</v>
+      </c>
       <c r="B43" s="9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
-        <v>1020001471</v>
+        <v>1020001609</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
-        <v>74648</v>
+        <v>1020000317</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
-        <v>1020001305</v>
+        <v>1020001570</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
-        <v>1020001308</v>
+        <v>1020001711</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
-        <v>297007</v>
+        <v>1020001712</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
-        <v>1020001037</v>
+        <v>1020001612</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
-        <v>1020000874</v>
+        <v>1020001713</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
-        <v>1030000556</v>
+        <v>1020001613</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
-        <v>1020001071</v>
+        <v>1020001714</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
-        <v>1020001092</v>
+        <v>1020001715</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
-        <v>1020001568</v>
+        <v>116762</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
-        <v>1020001569</v>
+        <v>1020001400</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
-        <v>1020001609</v>
+        <v>1020001366</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
-        <v>1020000317</v>
+        <v>1020001402</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
-        <v>1020001570</v>
+        <v>1020002010</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
-        <v>1020001711</v>
+        <v>201982</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
-        <v>1020001712</v>
+        <v>1020001559</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
-        <v>1020001612</v>
+        <v>1020001734</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
-        <v>1020001713</v>
+        <v>1020001735</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
-        <v>1020001613</v>
+        <v>1020001624</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
-        <v>1020001714</v>
+        <v>1020001625</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
-        <v>1020001715</v>
+        <v>1020001736</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
-        <v>116762</v>
+        <v>1020001678</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
-        <v>1020001400</v>
+        <v>1020001626</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
-        <v>1020001366</v>
+        <v>1020001679</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
-        <v>1020001402</v>
+        <v>1020001627</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
-        <v>1020002010</v>
+        <v>1020001737</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
-        <v>201982</v>
+        <v>1020001369</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
-        <v>1020001559</v>
+        <v>1020001370</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
-        <v>1020001734</v>
+        <v>1020001421</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
-        <v>1020001735</v>
+        <v>297451</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
-        <v>1020001624</v>
+        <v>1020001422</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
-        <v>1020001625</v>
+        <v>1020001423</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
-        <v>1020001736</v>
+        <v>1020001424</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
-        <v>1020001678</v>
+        <v>297455</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
-        <v>1020001626</v>
+        <v>297456</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
-        <v>1020001679</v>
+        <v>1020001276</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
-        <v>1020001627</v>
+        <v>1020001166</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
-        <v>1020001737</v>
+        <v>1020001137</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
-        <v>1020001369</v>
+        <v>397233</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
-        <v>1020001370</v>
+        <v>1030000472</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
-        <v>1020001421</v>
+        <v>1020001265</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
-        <v>297451</v>
+        <v>1020001042</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
-        <v>1020001422</v>
+        <v>1020001266</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
-        <v>1020001423</v>
+        <v>1020001263</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
-        <v>1020001424</v>
+        <v>306792</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
-        <v>297455</v>
+        <v>306791</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
-        <v>297456</v>
+        <v>306790</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
-        <v>1020001276</v>
+        <v>306788</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
-        <v>1020001166</v>
+        <v>41673</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
-        <v>1020001137</v>
+        <v>138818</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
-        <v>397233</v>
+        <v>138817</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
-        <v>1030000472</v>
+        <v>267476</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="9">
-        <v>1020001265</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="9">
-        <v>1020001042</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="9">
-        <v>1020001266</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="9">
-        <v>1020001263</v>
-      </c>
-      <c r="B100" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="9">
-        <v>1010038793</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="9">
-        <v>1010038792</v>
-      </c>
-      <c r="B102" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C102" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="9">
-        <v>1010038791</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="9">
-        <v>1010038790</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="9">
-        <v>1010038778</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="9">
-        <v>416724</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="9">
-        <v>145241</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="9">
-        <v>306792</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="9">
-        <v>306791</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="9">
-        <v>306790</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="9">
-        <v>306788</v>
-      </c>
-      <c r="B111" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="9">
-        <v>41673</v>
-      </c>
-      <c r="B112" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="9">
-        <v>138818</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="9">
-        <v>138817</v>
-      </c>
-      <c r="B114" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="9">
-        <v>267476</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="9">
-        <v>1010027124</v>
-      </c>
-      <c r="B116" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="9">
-        <v>1010027216</v>
-      </c>
-      <c r="B117" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="9">
-        <v>1010027215</v>
-      </c>
-      <c r="B118" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="9">
-        <v>1010027214</v>
-      </c>
-      <c r="B119" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="9">
-        <v>1010027084</v>
-      </c>
-      <c r="B120" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="9">
-        <v>1010027121</v>
-      </c>
-      <c r="B121" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="9">
-        <v>1010027118</v>
-      </c>
-      <c r="B122" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="9">
-        <v>1010027115</v>
-      </c>
-      <c r="B123" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="9">
-        <v>1010027117</v>
-      </c>
-      <c r="B124" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" s="9">
-        <v>1010027113</v>
-      </c>
-      <c r="B125" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="9">
-        <v>1010027112</v>
-      </c>
-      <c r="B126" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A127" s="9">
-        <v>1010027070</v>
-      </c>
-      <c r="B127" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+    </row>
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+    </row>
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+    </row>
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+    </row>
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+    </row>
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+    </row>
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+    </row>
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="2"/>
+      <c r="B104" s="6"/>
+    </row>
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+    </row>
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="2"/>
+      <c r="B106" s="6"/>
+    </row>
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+    </row>
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+    </row>
+    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+    </row>
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+    </row>
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+    </row>
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+    </row>
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+    </row>
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+    </row>
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+    </row>
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+    </row>
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+    </row>
+    <row r="118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+    </row>
+    <row r="119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+    </row>
+    <row r="120" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+    </row>
+    <row r="121" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+    </row>
+    <row r="122" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+    </row>
+    <row r="123" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+    </row>
+    <row r="124" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+    </row>
+    <row r="125" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
+    </row>
+    <row r="126" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+    </row>
+    <row r="127" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+    </row>
+    <row r="128" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
     </row>
@@ -2315,7 +2003,7 @@
     </row>
     <row r="135" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
-      <c r="B135" s="6"/>
+      <c r="B135" s="2"/>
     </row>
     <row r="136" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
@@ -3427,127 +3115,127 @@
     </row>
     <row r="413" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="2"/>
-      <c r="B413" s="2"/>
+      <c r="B413" s="1"/>
     </row>
     <row r="414" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="2"/>
-      <c r="B414" s="2"/>
+      <c r="B414" s="1"/>
     </row>
     <row r="415" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" s="2"/>
-      <c r="B415" s="2"/>
+      <c r="B415" s="1"/>
     </row>
     <row r="416" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" s="2"/>
-      <c r="B416" s="2"/>
+      <c r="B416" s="1"/>
     </row>
     <row r="417" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" s="2"/>
-      <c r="B417" s="2"/>
+      <c r="B417" s="1"/>
     </row>
     <row r="418" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="2"/>
-      <c r="B418" s="2"/>
+      <c r="B418" s="1"/>
     </row>
     <row r="419" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" s="2"/>
-      <c r="B419" s="2"/>
+      <c r="B419" s="1"/>
     </row>
     <row r="420" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="2"/>
-      <c r="B420" s="2"/>
+      <c r="B420" s="1"/>
     </row>
     <row r="421" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" s="2"/>
-      <c r="B421" s="2"/>
+      <c r="B421" s="1"/>
     </row>
     <row r="422" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" s="2"/>
-      <c r="B422" s="2"/>
+      <c r="B422" s="1"/>
     </row>
     <row r="423" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="2"/>
-      <c r="B423" s="2"/>
+      <c r="B423" s="1"/>
     </row>
     <row r="424" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" s="2"/>
-      <c r="B424" s="2"/>
+      <c r="B424" s="1"/>
     </row>
     <row r="425" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" s="2"/>
-      <c r="B425" s="2"/>
+      <c r="B425" s="1"/>
     </row>
     <row r="426" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" s="2"/>
-      <c r="B426" s="2"/>
+      <c r="B426" s="1"/>
     </row>
     <row r="427" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="2"/>
-      <c r="B427" s="2"/>
+      <c r="B427" s="1"/>
     </row>
     <row r="428" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="2"/>
-      <c r="B428" s="2"/>
+      <c r="B428" s="1"/>
     </row>
     <row r="429" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" s="2"/>
-      <c r="B429" s="2"/>
+      <c r="B429" s="1"/>
     </row>
     <row r="430" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" s="2"/>
-      <c r="B430" s="2"/>
+      <c r="B430" s="1"/>
     </row>
     <row r="431" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" s="2"/>
-      <c r="B431" s="2"/>
+      <c r="B431" s="1"/>
     </row>
     <row r="432" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" s="2"/>
-      <c r="B432" s="2"/>
+      <c r="B432" s="1"/>
     </row>
     <row r="433" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="2"/>
-      <c r="B433" s="2"/>
+      <c r="B433" s="1"/>
     </row>
     <row r="434" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="2"/>
-      <c r="B434" s="2"/>
+      <c r="B434" s="1"/>
     </row>
     <row r="435" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="2"/>
-      <c r="B435" s="2"/>
+      <c r="B435" s="1"/>
     </row>
     <row r="436" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="2"/>
-      <c r="B436" s="2"/>
+      <c r="B436" s="1"/>
     </row>
     <row r="437" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="2"/>
-      <c r="B437" s="2"/>
+      <c r="B437" s="1"/>
     </row>
     <row r="438" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" s="2"/>
-      <c r="B438" s="2"/>
+      <c r="B438" s="1"/>
     </row>
     <row r="439" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="2"/>
-      <c r="B439" s="2"/>
+      <c r="B439" s="1"/>
     </row>
     <row r="440" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="2"/>
-      <c r="B440" s="2"/>
+      <c r="B440" s="1"/>
     </row>
     <row r="441" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="2"/>
-      <c r="B441" s="2"/>
+      <c r="B441" s="1"/>
     </row>
     <row r="442" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="2"/>
-      <c r="B442" s="2"/>
+      <c r="B442" s="1"/>
     </row>
     <row r="443" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="2"/>
-      <c r="B443" s="2"/>
+      <c r="B443" s="1"/>
     </row>
     <row r="444" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="2"/>
@@ -3698,127 +3386,127 @@
       <c r="B480" s="1"/>
     </row>
     <row r="481" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A481" s="2"/>
+      <c r="A481" s="1"/>
       <c r="B481" s="1"/>
     </row>
     <row r="482" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A482" s="2"/>
+      <c r="A482" s="1"/>
       <c r="B482" s="1"/>
     </row>
     <row r="483" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="2"/>
+      <c r="A483" s="1"/>
       <c r="B483" s="1"/>
     </row>
     <row r="484" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="2"/>
+      <c r="A484" s="1"/>
       <c r="B484" s="1"/>
     </row>
     <row r="485" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A485" s="2"/>
+      <c r="A485" s="1"/>
       <c r="B485" s="1"/>
     </row>
     <row r="486" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A486" s="2"/>
+      <c r="A486" s="1"/>
       <c r="B486" s="1"/>
     </row>
     <row r="487" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A487" s="2"/>
+      <c r="A487" s="1"/>
       <c r="B487" s="1"/>
     </row>
     <row r="488" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A488" s="2"/>
+      <c r="A488" s="1"/>
       <c r="B488" s="1"/>
     </row>
     <row r="489" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A489" s="2"/>
+      <c r="A489" s="1"/>
       <c r="B489" s="1"/>
     </row>
     <row r="490" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A490" s="2"/>
+      <c r="A490" s="1"/>
       <c r="B490" s="1"/>
     </row>
     <row r="491" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A491" s="2"/>
+      <c r="A491" s="1"/>
       <c r="B491" s="1"/>
     </row>
     <row r="492" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A492" s="2"/>
+      <c r="A492" s="1"/>
       <c r="B492" s="1"/>
     </row>
     <row r="493" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A493" s="2"/>
+      <c r="A493" s="1"/>
       <c r="B493" s="1"/>
     </row>
     <row r="494" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A494" s="2"/>
+      <c r="A494" s="1"/>
       <c r="B494" s="1"/>
     </row>
     <row r="495" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A495" s="2"/>
+      <c r="A495" s="1"/>
       <c r="B495" s="1"/>
     </row>
     <row r="496" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A496" s="2"/>
+      <c r="A496" s="1"/>
       <c r="B496" s="1"/>
     </row>
     <row r="497" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A497" s="2"/>
+      <c r="A497" s="1"/>
       <c r="B497" s="1"/>
     </row>
     <row r="498" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A498" s="2"/>
+      <c r="A498" s="1"/>
       <c r="B498" s="1"/>
     </row>
     <row r="499" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A499" s="2"/>
+      <c r="A499" s="1"/>
       <c r="B499" s="1"/>
     </row>
     <row r="500" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A500" s="2"/>
+      <c r="A500" s="1"/>
       <c r="B500" s="1"/>
     </row>
     <row r="501" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A501" s="2"/>
+      <c r="A501" s="1"/>
       <c r="B501" s="1"/>
     </row>
     <row r="502" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A502" s="2"/>
+      <c r="A502" s="1"/>
       <c r="B502" s="1"/>
     </row>
     <row r="503" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A503" s="2"/>
+      <c r="A503" s="1"/>
       <c r="B503" s="1"/>
     </row>
     <row r="504" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A504" s="2"/>
+      <c r="A504" s="1"/>
       <c r="B504" s="1"/>
     </row>
     <row r="505" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A505" s="2"/>
+      <c r="A505" s="1"/>
       <c r="B505" s="1"/>
     </row>
     <row r="506" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A506" s="2"/>
+      <c r="A506" s="1"/>
       <c r="B506" s="1"/>
     </row>
     <row r="507" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A507" s="2"/>
+      <c r="A507" s="1"/>
       <c r="B507" s="1"/>
     </row>
     <row r="508" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A508" s="2"/>
+      <c r="A508" s="1"/>
       <c r="B508" s="1"/>
     </row>
     <row r="509" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A509" s="2"/>
+      <c r="A509" s="1"/>
       <c r="B509" s="1"/>
     </row>
     <row r="510" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A510" s="2"/>
+      <c r="A510" s="1"/>
       <c r="B510" s="1"/>
     </row>
     <row r="511" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A511" s="2"/>
+      <c r="A511" s="1"/>
       <c r="B511" s="1"/>
     </row>
     <row r="512" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4476,130 +4164,6 @@
     <row r="675" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
-    </row>
-    <row r="676" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A676" s="1"/>
-      <c r="B676" s="1"/>
-    </row>
-    <row r="677" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A677" s="1"/>
-      <c r="B677" s="1"/>
-    </row>
-    <row r="678" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A678" s="1"/>
-      <c r="B678" s="1"/>
-    </row>
-    <row r="679" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A679" s="1"/>
-      <c r="B679" s="1"/>
-    </row>
-    <row r="680" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A680" s="1"/>
-      <c r="B680" s="1"/>
-    </row>
-    <row r="681" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A681" s="1"/>
-      <c r="B681" s="1"/>
-    </row>
-    <row r="682" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A682" s="1"/>
-      <c r="B682" s="1"/>
-    </row>
-    <row r="683" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A683" s="1"/>
-      <c r="B683" s="1"/>
-    </row>
-    <row r="684" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A684" s="1"/>
-      <c r="B684" s="1"/>
-    </row>
-    <row r="685" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A685" s="1"/>
-      <c r="B685" s="1"/>
-    </row>
-    <row r="686" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A686" s="1"/>
-      <c r="B686" s="1"/>
-    </row>
-    <row r="687" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A687" s="1"/>
-      <c r="B687" s="1"/>
-    </row>
-    <row r="688" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A688" s="1"/>
-      <c r="B688" s="1"/>
-    </row>
-    <row r="689" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A689" s="1"/>
-      <c r="B689" s="1"/>
-    </row>
-    <row r="690" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A690" s="1"/>
-      <c r="B690" s="1"/>
-    </row>
-    <row r="691" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A691" s="1"/>
-      <c r="B691" s="1"/>
-    </row>
-    <row r="692" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A692" s="1"/>
-      <c r="B692" s="1"/>
-    </row>
-    <row r="693" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A693" s="1"/>
-      <c r="B693" s="1"/>
-    </row>
-    <row r="694" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A694" s="1"/>
-      <c r="B694" s="1"/>
-    </row>
-    <row r="695" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A695" s="1"/>
-      <c r="B695" s="1"/>
-    </row>
-    <row r="696" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A696" s="1"/>
-      <c r="B696" s="1"/>
-    </row>
-    <row r="697" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A697" s="1"/>
-      <c r="B697" s="1"/>
-    </row>
-    <row r="698" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A698" s="1"/>
-      <c r="B698" s="1"/>
-    </row>
-    <row r="699" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A699" s="1"/>
-      <c r="B699" s="1"/>
-    </row>
-    <row r="700" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A700" s="1"/>
-      <c r="B700" s="1"/>
-    </row>
-    <row r="701" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A701" s="1"/>
-      <c r="B701" s="1"/>
-    </row>
-    <row r="702" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A702" s="1"/>
-      <c r="B702" s="1"/>
-    </row>
-    <row r="703" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A703" s="1"/>
-      <c r="B703" s="1"/>
-    </row>
-    <row r="704" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A704" s="1"/>
-      <c r="B704" s="1"/>
-    </row>
-    <row r="705" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A705" s="1"/>
-      <c r="B705" s="1"/>
-    </row>
-    <row r="706" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A706" s="1"/>
-      <c r="B706" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
